--- a/artfynd/A 21097-2024 artfynd.xlsx
+++ b/artfynd/A 21097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118302374</v>
+        <v>118302133</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>90504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klingerhuvudberget (Klingerhuvudberget), Ång</t>
+          <t>Kälen (Kälen), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567016</v>
+        <v>567231</v>
       </c>
       <c r="R2" t="n">
-        <v>7061087</v>
+        <v>7060945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118301926</v>
+        <v>118302374</v>
       </c>
       <c r="B4" t="n">
         <v>79565</v>
@@ -935,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kälen (Kälen), Ång</t>
+          <t>Klingerhuvudberget (Klingerhuvudberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567176</v>
+        <v>567016</v>
       </c>
       <c r="R4" t="n">
-        <v>7060942</v>
+        <v>7061087</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118302133</v>
+        <v>118301926</v>
       </c>
       <c r="B5" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567231</v>
+        <v>567176</v>
       </c>
       <c r="R5" t="n">
-        <v>7060945</v>
+        <v>7060942</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 21097-2024 artfynd.xlsx
+++ b/artfynd/A 21097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118302133</v>
+        <v>118302697</v>
       </c>
       <c r="B2" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kälen (Kälen), Ång</t>
+          <t>Klingerhuvudberget (Klingerhuvudberget), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567231</v>
+        <v>566913</v>
       </c>
       <c r="R2" t="n">
-        <v>7060945</v>
+        <v>7061245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118302608</v>
+        <v>118302374</v>
       </c>
       <c r="B3" t="n">
-        <v>100080</v>
+        <v>79565</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1365</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566934</v>
+        <v>567016</v>
       </c>
       <c r="R3" t="n">
-        <v>7061200</v>
+        <v>7061087</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118302374</v>
+        <v>118301926</v>
       </c>
       <c r="B4" t="n">
         <v>79565</v>
@@ -935,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klingerhuvudberget (Klingerhuvudberget), Ång</t>
+          <t>Kälen (Kälen), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567016</v>
+        <v>567176</v>
       </c>
       <c r="R4" t="n">
-        <v>7061087</v>
+        <v>7060942</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118301926</v>
+        <v>118302608</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>100080</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kälen (Kälen), Ång</t>
+          <t>Klingerhuvudberget (Klingerhuvudberget), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567176</v>
+        <v>566934</v>
       </c>
       <c r="R5" t="n">
-        <v>7060942</v>
+        <v>7061200</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118302697</v>
+        <v>118302133</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>90504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klingerhuvudberget (Klingerhuvudberget), Ång</t>
+          <t>Kälen (Kälen), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566913</v>
+        <v>567231</v>
       </c>
       <c r="R6" t="n">
-        <v>7061245</v>
+        <v>7060945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21097-2024 artfynd.xlsx
+++ b/artfynd/A 21097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118302697</v>
+        <v>118302374</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566913</v>
+        <v>567016</v>
       </c>
       <c r="R2" t="n">
-        <v>7061245</v>
+        <v>7061087</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118302374</v>
+        <v>118302608</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>100087</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567016</v>
+        <v>566934</v>
       </c>
       <c r="R3" t="n">
-        <v>7061087</v>
+        <v>7061200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>118301926</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118302608</v>
+        <v>118302133</v>
       </c>
       <c r="B5" t="n">
-        <v>100080</v>
+        <v>90511</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klingerhuvudberget (Klingerhuvudberget), Ång</t>
+          <t>Kälen (Kälen), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566934</v>
+        <v>567231</v>
       </c>
       <c r="R5" t="n">
-        <v>7061200</v>
+        <v>7060945</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118302133</v>
+        <v>118302697</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
+        <v>79572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kälen (Kälen), Ång</t>
+          <t>Klingerhuvudberget (Klingerhuvudberget), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567231</v>
+        <v>566913</v>
       </c>
       <c r="R6" t="n">
-        <v>7060945</v>
+        <v>7061245</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
